--- a/management_forms/009_insider_risk_mitigation_assessment--management_forms.xlsx
+++ b/management_forms/009_insider_risk_mitigation_assessment--management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1194,8 +1194,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': '1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': '2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': '1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': '2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'financial',_'value':_'financial'}</t>
+          <t>financial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Financial', 'value': 'Financial'}</t>
+          <t>Financial</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'operational',_'value':_'operational'}</t>
+          <t>operational</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Operational', 'value': 'Operational'}</t>
+          <t>Operational</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'it',_'value':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'IT', 'value': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Open', 'value': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'malicious',_'value':_'malicious'}</t>
+          <t>malicious</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Malicious', 'value': 'Malicious'}</t>
+          <t>Malicious</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'accidental',_'value':_'accidental'}</t>
+          <t>accidental</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Accidental', 'value': 'Accidental'}</t>
+          <t>Accidental</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'insider',_'value':_'insider'}</t>
+          <t>insider</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Insider', 'value': 'Insider'}</t>
+          <t>Insider</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'outsider',_'value':_'outsider'}</t>
+          <t>outsider</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Outsider', 'value': 'Outsider'}</t>
+          <t>Outsider</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': '1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': '2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'not_closed',_'value':_'not_closed'}</t>
+          <t>not_closed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Not Closed', 'value': 'Not Closed'}</t>
+          <t>Not Closed</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'human_error',_'value':_'human_error'}</t>
+          <t>human_error</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Human error', 'value': 'Human error'}</t>
+          <t>Human error</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'system_error',_'value':_'system_error'}</t>
+          <t>system_error</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'System error', 'value': 'System error'}</t>
+          <t>System error</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'phishing',_'value':_'phishing'}</t>
+          <t>phishing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Phishing', 'value': 'Phishing'}</t>
+          <t>Phishing</t>
         </is>
       </c>
     </row>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'vishing',_'value':_'vishing'}</t>
+          <t>vishing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Vishing', 'value': 'Vishing'}</t>
+          <t>Vishing</t>
         </is>
       </c>
     </row>
